--- a/VibeProject1/Assets/Table/Item/TradeGoods.xlsx
+++ b/VibeProject1/Assets/Table/Item/TradeGoods.xlsx
@@ -1,69 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Merchant\VibeProject1\Assets\Table\Item\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6290F4-43EE-42B3-A1B4-5535D13B5886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
-    <sheet name="ItemStrings" sheetId="2" r:id="rId2"/>
+    <sheet name="ItemData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ItemStrings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>FootprintWidth</t>
-  </si>
-  <si>
-    <t>FootprintHeight</t>
-  </si>
-  <si>
-    <t>IconPath</t>
-  </si>
-  <si>
-    <t>gold-box</t>
-  </si>
-  <si>
-    <t>Ko</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,21 +54,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -384,65 +415,187 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col width="14.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.5" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FootprintWidth</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FootprintHeight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>IconPath</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gold-box</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>placeholder-1x1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>placeholder-2x1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="C2">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>placeholder-1x2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1</v>
       </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>placeholder-2x2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gold-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>placeholder-1x1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Placeholder 1x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>placeholder-2x1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Placeholder 2x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>placeholder-1x2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Placeholder 1x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>placeholder-2x2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Placeholder 2x2</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/VibeProject1/Assets/Table/Item/TradeGoods.xlsx
+++ b/VibeProject1/Assets/Table/Item/TradeGoods.xlsx
@@ -2,34 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ItemStrings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ItemDetail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ItemStrings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -57,7 +52,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,12 +415,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="14.875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15.5" bestFit="1" customWidth="1" min="3" max="3"/>
-  </cols>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -445,73 +436,72 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>IconPath</t>
+          <t>TradeKind</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gold-box</t>
+          <t>placeholder-1x1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>placeholder-1x1</t>
+          <t>placeholder-2x1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>placeholder-2x1</t>
+          <t>placeholder-1x2</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>placeholder-1x2</t>
+          <t>placeholder-2x2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>placeholder-2x2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -525,73 +515,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ItemId</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gold-box</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>placeholder-1x1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Placeholder 1x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>placeholder-2x1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Placeholder 2x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>placeholder-1x2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Placeholder 1x2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>placeholder-2x2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Placeholder 2x2</t>
         </is>
       </c>
     </row>

--- a/VibeProject1/Assets/Table/Item/TradeGoods.xlsx
+++ b/VibeProject1/Assets/Table/Item/TradeGoods.xlsx
@@ -1,129 +1,144 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="ItemData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ItemDetail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ItemStrings" sheetId="3" state="visible" r:id="rId3"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:workbookPr codeName="ThisWorkbook"/>
+  <x:workbookProtection/>
+  <x:bookViews>
+    <x:workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="ItemData" sheetId="1" r:id="rId1"/>
+    <x:sheet name="ItemDetail" sheetId="2" r:id="rId2"/>
+    <x:sheet name="ItemStrings" sheetId="3" r:id="rId3"/>
+  </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</x:workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>quest-box</x:t>
+  </x:si>
+</x:sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="0"/>
+  <x:fonts count="2">
+    <x:font>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:color theme="1"/>
+      <x:sz val="11"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </x:cellStyles>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,143 +425,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>FootprintWidth</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>FootprintHeight</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>TradeKind</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>placeholder-1x1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>placeholder-2x1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>placeholder-1x2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>placeholder-2x2</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D5"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>FootprintWidth</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>FootprintHeight</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>TradeKind</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0" t="inlineStr">
+        <x:is>
+          <x:t>placeholder-1x1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="0" t="inlineStr">
+        <x:is>
+          <x:t>placeholder-2x1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>placeholder-1x2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>placeholder-2x2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ItemId</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A1"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:1">
+      <x:c r="A1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>ItemId</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A1"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:1">
+      <x:c r="A1" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Id</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>